--- a/order_forms/044_kitchen_ventilation_filter_order_form--order_forms.xlsx
+++ b/order_forms/044_kitchen_ventilation_filter_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -603,7 +603,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HH:MM AM/PM</t>
+          <t>HH -MM AM/PM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ship To State</t>
+          <t>Ship To State 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -978,7 +978,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ship to City</t>
+          <t>Ship To City 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ship to State</t>
+          <t>Ship To State 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ship to Country</t>
+          <t>Ship To Country 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ship to Province</t>
+          <t>Ship To Province 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ship to Region</t>
+          <t>Ship To Region 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ship to Zip</t>
+          <t>Ship To Zip 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
